--- a/survey_templates/036_residential_soundproofing_satisfaction_survey--survey_templates.xlsx
+++ b/survey_templates/036_residential_soundproofing_satisfaction_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
